--- a/input/comparisons.xlsx
+++ b/input/comparisons.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanmaygandhi/Box Sync/runModac/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43314C77-6A9D-9A46-9882-113CA94DE469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275261F2-8A94-294A-A4B3-A143E83A2EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76800" yWindow="880" windowWidth="18760" windowHeight="19000" xr2:uid="{AC62268A-3574-A143-9B0A-533FA44997D6}"/>
+    <workbookView xWindow="76800" yWindow="880" windowWidth="10000" windowHeight="19000" xr2:uid="{AC62268A-3574-A143-9B0A-533FA44997D6}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="126">
   <si>
     <t>test</t>
   </si>
@@ -412,6 +412,9 @@
   </si>
   <si>
     <t>tab</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -939,8 +942,8 @@
       <c r="A7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B7" t="b">
-        <v>0</v>
+      <c r="B7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -956,7 +959,7 @@
         <v>123</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -964,7 +967,7 @@
         <v>122</v>
       </c>
       <c r="B10">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -972,7 +975,7 @@
         <v>121</v>
       </c>
       <c r="B11">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -980,7 +983,7 @@
         <v>120</v>
       </c>
       <c r="B12">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
